--- a/docs/Weekly-FYP-Diary.xlsx
+++ b/docs/Weekly-FYP-Diary.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\katie\Documents\GitHub\FinalYearProject\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\katie\Documents\GitHub\FinalYearProject\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{442202B4-8F96-4387-9E4E-7139C4A51464}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DDDBC404-B8A0-4C0D-9D9B-6D0A61FD9115}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{887A0C9C-0699-45CF-AAE2-6852A3FC5256}"/>
+    <workbookView xWindow="4008" yWindow="3720" windowWidth="17280" windowHeight="9960" xr2:uid="{887A0C9C-0699-45CF-AAE2-6852A3FC5256}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3" uniqueCount="3">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4" uniqueCount="4">
   <si>
     <t>Date:</t>
   </si>
@@ -48,6 +48,9 @@
   </si>
   <si>
     <t>Set up windows VM and made dummy files</t>
+  </si>
+  <si>
+    <t>Added dummy Office files</t>
   </si>
 </sst>
 </file>
@@ -437,7 +440,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2EDBC74A-DA46-4D76-8CDC-5F8DA65D05B0}">
-  <dimension ref="B2:C3"/>
+  <dimension ref="B2:C4"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="11.33203125" customWidth="1"/>
@@ -460,6 +463,14 @@
         <v>2</v>
       </c>
     </row>
+    <row r="4" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B4" s="1">
+        <v>46315</v>
+      </c>
+      <c r="C4" t="s">
+        <v>3</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
